--- a/data/gravel/Comotion Klatch 2025.xlsx
+++ b/data/gravel/Comotion Klatch 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E00E3A4-FE2C-734C-BE2B-7F39E9B09C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408904FC-80A7-6141-8055-4B1A969D3C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37060" yWindow="-23360" windowWidth="27760" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33480" yWindow="-23360" windowWidth="27760" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
   <si>
     <t>brand</t>
   </si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t>external</t>
+  </si>
+  <si>
+    <t>https://co-motion.com/cdn/shop/files/Klatch1600.jpg?v=1757454782</t>
   </si>
 </sst>
 </file>
@@ -733,6 +736,11 @@
         <v>90</v>
       </c>
     </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
@@ -835,7 +843,7 @@
         <v>77</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" ref="C10:C21" si="1">K10*10</f>
+        <f t="shared" ref="C10:C19" si="1">K10*10</f>
         <v>410</v>
       </c>
       <c r="D10" s="1">
@@ -892,31 +900,31 @@
         <v>78</v>
       </c>
       <c r="C11" s="1">
-        <f>K11</f>
+        <f t="shared" ref="C11:C17" si="2">K11</f>
         <v>115</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" ref="D11:I17" si="2">L11</f>
+        <f t="shared" ref="D11:I17" si="3">L11</f>
         <v>115</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>125</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>145</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>165</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>185</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>205</v>
       </c>
       <c r="K11" s="1">
@@ -949,31 +957,31 @@
         <v>79</v>
       </c>
       <c r="C12" s="1">
-        <f>K12</f>
-        <v>432</v>
-      </c>
-      <c r="D12" s="1">
         <f t="shared" si="2"/>
         <v>432</v>
       </c>
+      <c r="D12" s="1">
+        <f t="shared" si="3"/>
+        <v>432</v>
+      </c>
       <c r="E12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>432</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>432</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>432</v>
       </c>
       <c r="H12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>432</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>432</v>
       </c>
       <c r="K12" s="1">
@@ -1006,31 +1014,31 @@
         <v>80</v>
       </c>
       <c r="C13" s="1">
-        <f>K13</f>
+        <f t="shared" si="2"/>
         <v>75.5</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="E13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74.5</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74.5</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74</v>
       </c>
       <c r="I13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>73</v>
       </c>
       <c r="K13" s="1">
@@ -1063,31 +1071,31 @@
         <v>81</v>
       </c>
       <c r="C14" s="1">
-        <f>K14</f>
-        <v>395</v>
-      </c>
-      <c r="D14" s="1">
         <f t="shared" si="2"/>
         <v>395</v>
       </c>
+      <c r="D14" s="1">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
       <c r="E14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>395</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>395</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>395</v>
       </c>
       <c r="H14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>395</v>
       </c>
       <c r="I14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>395</v>
       </c>
       <c r="K14" s="1">
@@ -1120,31 +1128,31 @@
         <v>82</v>
       </c>
       <c r="C15" s="1">
-        <f>K15</f>
-        <v>71</v>
-      </c>
-      <c r="D15" s="1">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
+      <c r="D15" s="1">
+        <f t="shared" si="3"/>
+        <v>71</v>
+      </c>
       <c r="E15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71.5</v>
       </c>
       <c r="H15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71.5</v>
       </c>
       <c r="I15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71.5</v>
       </c>
       <c r="K15" s="1">
@@ -1177,31 +1185,31 @@
         <v>83</v>
       </c>
       <c r="C16" s="1">
-        <f>K16</f>
-        <v>47</v>
-      </c>
-      <c r="D16" s="1">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
+      <c r="D16" s="1">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
       <c r="E16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="H16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="I16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="K16" s="1">
@@ -1234,31 +1242,31 @@
         <v>84</v>
       </c>
       <c r="C17" s="1">
-        <f>K17</f>
-        <v>72</v>
-      </c>
-      <c r="D17" s="1">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
+      <c r="D17" s="1">
+        <f t="shared" si="3"/>
+        <v>72</v>
+      </c>
       <c r="E17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="H17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="I17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="K17" s="1">
@@ -1295,27 +1303,27 @@
         <v>691</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" ref="D18:I19" si="3">L18*10</f>
+        <f t="shared" ref="D18:I19" si="4">L18*10</f>
         <v>714</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>742</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>774</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>791</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>807</v>
       </c>
       <c r="I18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>826</v>
       </c>
       <c r="K18" s="1">
@@ -1352,27 +1360,27 @@
         <v>1010</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1010</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1010</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1030</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1040</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1050</v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1050</v>
       </c>
       <c r="K19" s="1">
@@ -1409,27 +1417,27 @@
         <v>543</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" ref="D20:I21" si="4">L20</f>
+        <f t="shared" ref="D20:I21" si="5">L20</f>
         <v>543</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>555</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>575</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>594</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>611</v>
       </c>
       <c r="I20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>630</v>
       </c>
       <c r="K20" s="1">
@@ -1466,27 +1474,27 @@
         <v>370</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>370</v>
       </c>
       <c r="E21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>367</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>381</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>387</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>393</v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>386</v>
       </c>
       <c r="K21" s="1">

--- a/data/gravel/Comotion Klatch 2025.xlsx
+++ b/data/gravel/Comotion Klatch 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408904FC-80A7-6141-8055-4B1A969D3C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EE610E-2904-534A-82CE-AF1059FDAFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33480" yWindow="-23360" windowWidth="27760" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -254,9 +254,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Co-Motion</t>
   </si>
   <si>
@@ -339,6 +336,15 @@
   </si>
   <si>
     <t>https://co-motion.com/cdn/shop/files/Klatch1600.jpg?v=1757454782</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Eugene, Oregon, USA</t>
   </si>
 </sst>
 </file>
@@ -689,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -701,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -709,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -733,12 +739,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -746,7 +752,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -754,28 +760,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -783,7 +789,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1">
         <f>K9*10</f>
@@ -840,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" ref="C10:C19" si="1">K10*10</f>
@@ -897,7 +903,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" ref="C11:C17" si="2">K11</f>
@@ -954,7 +960,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="2"/>
@@ -1011,7 +1017,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="2"/>
@@ -1068,7 +1074,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="2"/>
@@ -1125,7 +1131,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="2"/>
@@ -1182,7 +1188,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="2"/>
@@ -1239,7 +1245,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="2"/>
@@ -1296,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" s="1">
         <f>K18*10</f>
@@ -1353,7 +1359,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
@@ -1410,7 +1416,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C20" s="1">
         <f>K20</f>
@@ -1467,7 +1473,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C21" s="1">
         <f>K21</f>
@@ -1682,7 +1688,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1800,7 +1806,7 @@
         <v>51</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1894,7 +1900,15 @@
         <v>65</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>73</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Comotion Klatch 2025.xlsx
+++ b/data/gravel/Comotion Klatch 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EE610E-2904-534A-82CE-AF1059FDAFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3EB708-F3F7-E242-AF1A-6B5B4F9E8FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33480" yWindow="-23360" windowWidth="27760" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,24 @@
   </si>
   <si>
     <t>Eugene, Oregon, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -695,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1752,162 +1770,192 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="1">
-        <v>27.2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B55" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B66" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B67" s="1">
-        <v>3095</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B68" s="1">
-        <v>5395</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="1">
+        <v>3095</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1">
+        <v>5395</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>103</v>
       </c>
     </row>
